--- a/Documentation/Iteration 2/Gantt Chart.xlsx
+++ b/Documentation/Iteration 2/Gantt Chart.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD47FCF-D0F8-894E-B66B-2DF274949653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB98E5B-4412-45E0-9352-1386CE258781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3480" yWindow="740" windowWidth="39760" windowHeight="23780" tabRatio="415" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12396" tabRatio="415" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dark" sheetId="16" r:id="rId1"/>
@@ -192,9 +192,6 @@
     <t>User Acceptance Testing</t>
   </si>
   <si>
-    <t>Review</t>
-  </si>
-  <si>
     <t>I3 Progress Report / Quiz</t>
   </si>
   <si>
@@ -206,14 +203,17 @@
   <si>
     <t>Agile Projects - Gantt Chart</t>
   </si>
+  <si>
+    <t>Review I3 and Submit</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="d"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="d"/>
   </numFmts>
   <fonts count="27" x14ac:knownFonts="1">
     <font>
@@ -632,7 +632,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="1" applyFont="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyFont="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyProtection="0">
@@ -684,10 +684,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -738,13 +738,13 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -801,7 +801,7 @@
     <xf numFmtId="37" fontId="0" fillId="9" borderId="0" xfId="10" applyFont="1" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -814,7 +814,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -829,19 +829,19 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="8" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
@@ -856,14 +856,14 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -876,7 +876,7 @@
     <cellStyle name="Heading 3" xfId="8" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="2" builtinId="5" customBuiltin="1"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5" customBuiltin="1"/>
     <cellStyle name="Title" xfId="5" builtinId="15" customBuiltin="1"/>
     <cellStyle name="zHiddenText" xfId="3" xr:uid="{26E66EE6-E33F-4D77-BAE4-0FB4F5BBF673}"/>
   </cellStyles>
@@ -1447,13 +1447,13 @@
           <xdr:col>8</xdr:col>
           <xdr:colOff>38100</xdr:colOff>
           <xdr:row>7</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
+          <xdr:rowOff>60960</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>63</xdr:col>
           <xdr:colOff>228600</xdr:colOff>
           <xdr:row>7</xdr:row>
-          <xdr:rowOff>241300</xdr:rowOff>
+          <xdr:rowOff>243840</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1463,7 +1463,7 @@
                   <a14:compatExt spid="_x0000_s13313"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000001340000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001340000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1787,25 +1787,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BP43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" style="6" customWidth="1"/>
     <col min="2" max="2" width="30.6640625" customWidth="1"/>
     <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.5" customWidth="1"/>
+    <col min="4" max="4" width="20.44140625" customWidth="1"/>
     <col min="5" max="5" width="15.6640625" customWidth="1"/>
-    <col min="6" max="6" width="10.5" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.5" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="10.44140625" customWidth="1"/>
     <col min="8" max="8" width="2.6640625" customWidth="1"/>
-    <col min="9" max="64" width="3.5" customWidth="1"/>
+    <col min="9" max="64" width="3.44140625" customWidth="1"/>
     <col min="65" max="65" width="2.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="25.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="1:68" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:68" ht="25.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:68" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="70" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C2" s="70"/>
       <c r="D2" s="70"/>
@@ -1871,7 +1871,7 @@
       <c r="BL2" s="17"/>
       <c r="BM2" s="17"/>
     </row>
-    <row r="3" spans="1:68" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:68" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="38"/>
       <c r="C3" s="39"/>
@@ -1938,10 +1938,10 @@
       <c r="BL3" s="28"/>
       <c r="BM3" s="28"/>
     </row>
-    <row r="4" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7"/>
       <c r="B4" s="50" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="47"/>
@@ -1951,40 +1951,40 @@
         <v>10</v>
       </c>
       <c r="H4" s="25"/>
-      <c r="I4" s="67" t="s">
+      <c r="I4" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
+      <c r="J4" s="74"/>
+      <c r="K4" s="74"/>
+      <c r="L4" s="74"/>
       <c r="M4" s="28"/>
-      <c r="N4" s="68" t="s">
+      <c r="N4" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="O4" s="68"/>
-      <c r="P4" s="68"/>
-      <c r="Q4" s="68"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
       <c r="R4" s="28"/>
-      <c r="S4" s="69" t="s">
+      <c r="S4" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="T4" s="69"/>
-      <c r="U4" s="69"/>
-      <c r="V4" s="69"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
       <c r="W4" s="28"/>
-      <c r="X4" s="65" t="s">
+      <c r="X4" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="Y4" s="65"/>
-      <c r="Z4" s="65"/>
-      <c r="AA4" s="65"/>
+      <c r="Y4" s="68"/>
+      <c r="Z4" s="68"/>
+      <c r="AA4" s="68"/>
       <c r="AB4" s="28"/>
-      <c r="AC4" s="66" t="s">
+      <c r="AC4" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="AD4" s="66"/>
-      <c r="AE4" s="66"/>
-      <c r="AF4" s="66"/>
+      <c r="AD4" s="69"/>
+      <c r="AE4" s="69"/>
+      <c r="AF4" s="69"/>
       <c r="AG4" s="28"/>
       <c r="AH4" s="28"/>
       <c r="AI4" s="28"/>
@@ -2019,10 +2019,10 @@
       <c r="BL4" s="28"/>
       <c r="BM4" s="28"/>
     </row>
-    <row r="5" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="51" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C5" s="48"/>
       <c r="D5" s="48"/>
@@ -2088,7 +2088,7 @@
       <c r="BL5" s="28"/>
       <c r="BM5" s="28"/>
     </row>
-    <row r="6" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="7"/>
       <c r="B6" s="45" t="s">
         <v>9</v>
@@ -2184,7 +2184,7 @@
       <c r="BL6" s="56"/>
       <c r="BM6" s="28"/>
     </row>
-    <row r="7" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="45" t="s">
         <v>5</v>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="BM7" s="28"/>
     </row>
-    <row r="8" spans="1:68" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:68" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="47"/>
       <c r="C8" s="47"/>
@@ -2490,7 +2490,7 @@
       <c r="BL8" s="35"/>
       <c r="BM8" s="28"/>
     </row>
-    <row r="9" spans="1:68" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:68" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="62" t="s">
         <v>13</v>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="BM9" s="28"/>
     </row>
-    <row r="10" spans="1:68" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="13"/>
       <c r="C10" s="10"/>
       <c r="D10" s="9"/>
@@ -2803,7 +2803,7 @@
       <c r="BL10" s="32"/>
       <c r="BM10" s="28"/>
     </row>
-    <row r="11" spans="1:68" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:68" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="64" t="s">
         <v>20</v>
@@ -3045,7 +3045,7 @@
       <c r="BM11" s="24"/>
       <c r="BP11" s="37"/>
     </row>
-    <row r="12" spans="1:68" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:68" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
       <c r="B12" s="22" t="s">
         <v>21</v>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="BM12" s="24"/>
     </row>
-    <row r="13" spans="1:68" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:68" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
       <c r="B13" s="22" t="s">
         <v>23</v>
@@ -3539,9 +3539,9 @@
       </c>
       <c r="BM13" s="24"/>
     </row>
-    <row r="14" spans="1:68" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:68" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
-      <c r="B14" s="74" t="s">
+      <c r="B14" s="65" t="s">
         <v>25</v>
       </c>
       <c r="C14" s="18" t="s">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="BM14" s="24"/>
     </row>
-    <row r="15" spans="1:68" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:68" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="22" t="s">
         <v>26</v>
@@ -4033,9 +4033,9 @@
       </c>
       <c r="BM15" s="24"/>
     </row>
-    <row r="16" spans="1:68" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:68" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6"/>
-      <c r="B16" s="74" t="s">
+      <c r="B16" s="65" t="s">
         <v>27</v>
       </c>
       <c r="C16" s="18" t="s">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="BM16" s="24"/>
     </row>
-    <row r="17" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:65" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
       <c r="B17" s="22" t="s">
         <v>28</v>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="BM17" s="24"/>
     </row>
-    <row r="18" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:65" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7"/>
       <c r="B18" s="22" t="s">
         <v>29</v>
@@ -4774,9 +4774,9 @@
       </c>
       <c r="BM18" s="24"/>
     </row>
-    <row r="19" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:65" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6"/>
-      <c r="B19" s="74" t="s">
+      <c r="B19" s="65" t="s">
         <v>30</v>
       </c>
       <c r="C19" s="18" t="s">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="BM19" s="24"/>
     </row>
-    <row r="20" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:65" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="64" t="s">
         <v>31</v>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="BM20" s="24"/>
     </row>
-    <row r="21" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:65" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6"/>
       <c r="B21" s="22" t="s">
         <v>32</v>
@@ -5509,9 +5509,9 @@
       </c>
       <c r="BM21" s="24"/>
     </row>
-    <row r="22" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:65" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
-      <c r="B22" s="75" t="s">
+      <c r="B22" s="66" t="s">
         <v>34</v>
       </c>
       <c r="C22" s="18" t="s">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="BM22" s="24"/>
     </row>
-    <row r="23" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:65" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6"/>
       <c r="B23" s="22" t="s">
         <v>35</v>
@@ -6003,9 +6003,9 @@
       </c>
       <c r="BM23" s="24"/>
     </row>
-    <row r="24" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:65" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
-      <c r="B24" s="74" t="s">
+      <c r="B24" s="65" t="s">
         <v>36</v>
       </c>
       <c r="C24" s="18" t="s">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="BM24" s="24"/>
     </row>
-    <row r="25" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:65" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6"/>
       <c r="B25" s="22" t="s">
         <v>37</v>
@@ -6497,9 +6497,9 @@
       </c>
       <c r="BM25" s="24"/>
     </row>
-    <row r="26" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:65" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
-      <c r="B26" s="74" t="s">
+      <c r="B26" s="65" t="s">
         <v>38</v>
       </c>
       <c r="C26" s="18" t="s">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="BM26" s="24"/>
     </row>
-    <row r="27" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:65" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="22" t="s">
         <v>39</v>
@@ -6756,7 +6756,7 @@
         <v>24</v>
       </c>
       <c r="E27" s="19">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F27" s="20">
         <v>46111</v>
@@ -6991,9 +6991,9 @@
       </c>
       <c r="BM27" s="24"/>
     </row>
-    <row r="28" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:65" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
-      <c r="B28" s="74" t="s">
+      <c r="B28" s="65" t="s">
         <v>40</v>
       </c>
       <c r="C28" s="18" t="s">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="BM28" s="24"/>
     </row>
-    <row r="29" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:65" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
       <c r="B29" s="22" t="s">
         <v>41</v>
@@ -7481,9 +7481,9 @@
       </c>
       <c r="BM29" s="24"/>
     </row>
-    <row r="30" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:65" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
-      <c r="B30" s="74" t="s">
+      <c r="B30" s="65" t="s">
         <v>42</v>
       </c>
       <c r="C30" s="18" t="s">
@@ -7492,7 +7492,9 @@
       <c r="D30" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E30" s="19"/>
+      <c r="E30" s="19">
+        <v>1</v>
+      </c>
       <c r="F30" s="20">
         <v>46139</v>
       </c>
@@ -7726,7 +7728,7 @@
       </c>
       <c r="BM30" s="24"/>
     </row>
-    <row r="31" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:65" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="B31" s="64" t="s">
         <v>43</v>
@@ -7967,7 +7969,7 @@
       </c>
       <c r="BM31" s="24"/>
     </row>
-    <row r="32" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:65" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
       <c r="B32" s="22" t="s">
         <v>44</v>
@@ -7978,7 +7980,9 @@
       <c r="D32" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="19"/>
+      <c r="E32" s="19">
+        <v>1</v>
+      </c>
       <c r="F32" s="20">
         <v>46141</v>
       </c>
@@ -8212,7 +8216,7 @@
       </c>
       <c r="BM32" s="24"/>
     </row>
-    <row r="33" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:65" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
       <c r="B33" s="22" t="s">
         <v>46</v>
@@ -8223,7 +8227,9 @@
       <c r="D33" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E33" s="19"/>
+      <c r="E33" s="19">
+        <v>1</v>
+      </c>
       <c r="F33" s="20">
         <v>46147</v>
       </c>
@@ -8457,9 +8463,9 @@
       </c>
       <c r="BM33" s="24"/>
     </row>
-    <row r="34" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:65" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6"/>
-      <c r="B34" s="74" t="s">
+      <c r="B34" s="65" t="s">
         <v>47</v>
       </c>
       <c r="C34" s="18" t="s">
@@ -8468,7 +8474,9 @@
       <c r="D34" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E34" s="19"/>
+      <c r="E34" s="19">
+        <v>1</v>
+      </c>
       <c r="F34" s="20">
         <v>46148</v>
       </c>
@@ -8702,7 +8710,7 @@
       </c>
       <c r="BM34" s="24"/>
     </row>
-    <row r="35" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:65" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6"/>
       <c r="B35" s="22" t="s">
         <v>48</v>
@@ -8713,7 +8721,9 @@
       <c r="D35" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E35" s="19"/>
+      <c r="E35" s="19">
+        <v>1</v>
+      </c>
       <c r="F35" s="20">
         <v>46149</v>
       </c>
@@ -8779,9 +8789,9 @@
       <c r="BL35" s="23"/>
       <c r="BM35" s="24"/>
     </row>
-    <row r="36" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:65" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6"/>
-      <c r="B36" s="74" t="s">
+      <c r="B36" s="65" t="s">
         <v>49</v>
       </c>
       <c r="C36" s="18" t="s">
@@ -8790,7 +8800,9 @@
       <c r="D36" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E36" s="19"/>
+      <c r="E36" s="19">
+        <v>1</v>
+      </c>
       <c r="F36" s="20">
         <v>46154</v>
       </c>
@@ -8856,9 +8868,9 @@
       <c r="BL36" s="23"/>
       <c r="BM36" s="24"/>
     </row>
-    <row r="37" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:65" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6"/>
-      <c r="B37" s="76" t="s">
+      <c r="B37" s="67" t="s">
         <v>47</v>
       </c>
       <c r="C37" s="18" t="s">
@@ -8867,7 +8879,9 @@
       <c r="D37" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="19"/>
+      <c r="E37" s="19">
+        <v>1</v>
+      </c>
       <c r="F37" s="20">
         <v>46155</v>
       </c>
@@ -8933,7 +8947,7 @@
       <c r="BL37" s="23"/>
       <c r="BM37" s="24"/>
     </row>
-    <row r="38" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:65" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6"/>
       <c r="B38" s="22" t="s">
         <v>50</v>
@@ -8946,7 +8960,7 @@
       </c>
       <c r="E38" s="19"/>
       <c r="F38" s="20">
-        <v>46156</v>
+        <v>46161</v>
       </c>
       <c r="G38" s="21">
         <v>4</v>
@@ -9010,10 +9024,10 @@
       <c r="BL38" s="23"/>
       <c r="BM38" s="24"/>
     </row>
-    <row r="39" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:65" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6"/>
       <c r="B39" s="22" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C39" s="18" t="s">
         <v>1</v>
@@ -9087,10 +9101,10 @@
       <c r="BL39" s="23"/>
       <c r="BM39" s="24"/>
     </row>
-    <row r="40" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:65" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6"/>
       <c r="B40" s="22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C40" s="18" t="s">
         <v>2</v>
@@ -9332,7 +9346,7 @@
       </c>
       <c r="BM40" s="57"/>
     </row>
-    <row r="41" spans="1:65" s="1" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:65" s="1" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7"/>
       <c r="B41" s="61" t="s">
         <v>12</v>
@@ -9401,12 +9415,12 @@
       <c r="BL41" s="52"/>
       <c r="BM41" s="24"/>
     </row>
-    <row r="42" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D42" s="4"/>
       <c r="G42" s="8"/>
       <c r="H42" s="3"/>
     </row>
-    <row r="43" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D43" s="5"/>
     </row>
   </sheetData>
@@ -9430,6 +9444,20 @@
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
           <x14:id>{834F9758-0C1F-4D2E-9A51-487C20C6A718}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E11:E40">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color theme="6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{6C7BF365-1E83-F943-9FE1-6B394E2CCB50}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -9488,20 +9516,6 @@
       <formula>AND(J$7&lt;=EOMONTH($I$7,2),J$7&gt;EOMONTH($I$7,0),J$7&gt;EOMONTH($I$7,1))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E11:E40">
-    <cfRule type="dataBar" priority="1">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="1"/>
-        <color theme="6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6C7BF365-1E83-F943-9FE1-6B394E2CCB50}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="13">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="C11" xr:uid="{5E1071E8-D9FB-2241-876E-284A5D5FA183}">
       <formula1>"Goal,Milestone,On Track, Low Risk, Med Risk, High Risk"</formula1>
@@ -9543,13 +9557,13 @@
                     <xdr:col>8</xdr:col>
                     <xdr:colOff>38100</xdr:colOff>
                     <xdr:row>7</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
+                    <xdr:rowOff>60960</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>63</xdr:col>
                     <xdr:colOff>228600</xdr:colOff>
                     <xdr:row>7</xdr:row>
-                    <xdr:rowOff>241300</xdr:rowOff>
+                    <xdr:rowOff>243840</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -9579,6 +9593,21 @@
             </x14:dataBar>
           </x14:cfRule>
           <xm:sqref>E9:E10 E41</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{6C7BF365-1E83-F943-9FE1-6B394E2CCB50}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E11:E40</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="7" id="{C84307BC-4E4D-4989-9D21-88D6AEB0AFD2}">
@@ -9618,21 +9647,6 @@
           </x14:cfRule>
           <xm:sqref>I41:BL41</xm:sqref>
         </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6C7BF365-1E83-F943-9FE1-6B394E2CCB50}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>E11:E40</xm:sqref>
-        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
@@ -9659,15 +9673,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="22a266b9fa9a230c5a512669d8b298c3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="eddc33fff6b14141ee5c74a0d29ea6a1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -9943,6 +9948,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA4BA2A8-DB97-40F9-8DB6-154C09C7467C}">
   <ds:schemaRefs>
@@ -9956,14 +9970,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39060724-9CA2-4290-8A0C-B53624A594E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75C87518-DD8E-42CD-8DAC-291A323E849B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9982,4 +9988,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39060724-9CA2-4290-8A0C-B53624A594E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Documentation/Iteration 2/Gantt Chart.xlsx
+++ b/Documentation/Iteration 2/Gantt Chart.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB98E5B-4412-45E0-9352-1386CE258781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDBCCD22-2488-46F4-A23C-9926E0EF0B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12396" tabRatio="415" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5521,7 +5521,7 @@
         <v>22</v>
       </c>
       <c r="E22" s="19">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F22" s="20">
         <v>46104</v>
@@ -5768,7 +5768,7 @@
         <v>33</v>
       </c>
       <c r="E23" s="19">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F23" s="20">
         <v>46105</v>
@@ -8958,7 +8958,9 @@
       <c r="D38" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E38" s="19"/>
+      <c r="E38" s="19">
+        <v>1</v>
+      </c>
       <c r="F38" s="20">
         <v>46161</v>
       </c>
@@ -9035,7 +9037,9 @@
       <c r="D39" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E39" s="19"/>
+      <c r="E39" s="19">
+        <v>1</v>
+      </c>
       <c r="F39" s="20">
         <v>46168</v>
       </c>
@@ -9112,7 +9116,9 @@
       <c r="D40" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E40" s="19"/>
+      <c r="E40" s="19">
+        <v>1</v>
+      </c>
       <c r="F40" s="20">
         <v>46169</v>
       </c>
@@ -9673,6 +9679,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="22a266b9fa9a230c5a512669d8b298c3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="eddc33fff6b14141ee5c74a0d29ea6a1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -9948,15 +9963,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA4BA2A8-DB97-40F9-8DB6-154C09C7467C}">
   <ds:schemaRefs>
@@ -9970,6 +9976,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39060724-9CA2-4290-8A0C-B53624A594E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75C87518-DD8E-42CD-8DAC-291A323E849B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9988,12 +10002,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39060724-9CA2-4290-8A0C-B53624A594E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>